--- a/data/trans_orig/IP07A19-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A19-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>36779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29285</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>42704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>44080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62138</t>
+          <t>62885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82758</t>
+          <t>82494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>29502</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10808</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14225</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>21481</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42649</t>
+          <t>42624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61535</t>
+          <t>62650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45930</t>
+          <t>45511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62151</t>
+          <t>62468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34163</t>
+          <t>34196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49281</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83993</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107703</t>
+          <t>106770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>46722</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17784</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13018</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48729</t>
+          <t>48039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17821</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>29950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>36037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44282</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14956</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23700</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>36058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35396</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>17719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41351</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46036</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53358</t>
+          <t>53467</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71106</t>
+          <t>71627</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93877</t>
+          <t>94700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23905</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>26610</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28453</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>46361</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13720</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>85173</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110797</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>63538</t>
+          <t>63770</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89369</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154169</t>
+          <t>155151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>191702</t>
+          <t>190342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>136482</t>
+          <t>137355</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>166385</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,82 +3588,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>152606</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>137586</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>167172</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>40,04%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>48,65%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>304175</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>282951</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>326760</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>42,63%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>152606</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>138574</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>167432</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>40,33%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>304175</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>282896</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>325099</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>61473</t>
+          <t>60500</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>71119</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94924</t>
+          <t>97400</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>116438</t>
+          <t>117505</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>150349</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15516</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40791</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32088</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38842</t>
+          <t>39477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52653</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72389</t>
+          <t>73424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22477</t>
+          <t>22444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36489</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45580</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9256</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33045</t>
+          <t>32540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47745</t>
+          <t>47387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>21380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36767</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58419</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79299</t>
+          <t>80051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45210</t>
+          <t>44930</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>35904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50926</t>
+          <t>50956</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69755</t>
+          <t>69506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91830</t>
+          <t>91719</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,03%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>22565</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>8062</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20473</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>38449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72818</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,27%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44867</t>
+          <t>45125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15872</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14535</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23675</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39695</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34914</t>
+          <t>35486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>49430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70626</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35121</t>
+          <t>34102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51468</t>
+          <t>51670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33298</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49293</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72867</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97251</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12220</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25081</t>
+          <t>25036</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22691</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120095</t>
+          <t>120696</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>149921</t>
+          <t>149292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>104501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134157</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>231952</t>
+          <t>233502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>272900</t>
+          <t>273217</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111005</t>
+          <t>111892</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140054</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>116244</t>
+          <t>117260</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>146264</t>
+          <t>147285</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>237775</t>
+          <t>238457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>278430</t>
+          <t>279346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32896</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>40144</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>78422</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>106689</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16071</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>43643</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11752</t>
+          <t>11985</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25407</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>19425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35013</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35329</t>
+          <t>34902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63914</t>
+          <t>64877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,91%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>19691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>43187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63490</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17282</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32726</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33709</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49839</t>
+          <t>49869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31867</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48104</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>69355</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>93100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36607</t>
+          <t>37058</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53644</t>
+          <t>53355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75939</t>
+          <t>75800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98462</t>
+          <t>98656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>12207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24457</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25048</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26911</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>48752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67746</t>
+          <t>68431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30796</t>
+          <t>30583</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20770</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42083</t>
+          <t>42382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>62148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19995</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24426</t>
+          <t>23567</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>40328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>42191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59425</t>
+          <t>59767</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43266</t>
+          <t>43166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74478</t>
+          <t>73700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97835</t>
+          <t>98445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>48964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47649</t>
+          <t>47416</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67127</t>
+          <t>66790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90897</t>
+          <t>90780</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,43%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26639</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22846</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>41454</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>134608</t>
+          <t>135310</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164484</t>
+          <t>165324</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>114494</t>
+          <t>114693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>144312</t>
+          <t>144308</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>255471</t>
+          <t>256098</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>300320</t>
+          <t>299026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117130</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146496</t>
+          <t>147470</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125131</t>
+          <t>124475</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>156677</t>
+          <t>154859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>248439</t>
+          <t>251404</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>294022</t>
+          <t>292480</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>44990</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67588</t>
+          <t>67441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54409</t>
+          <t>55405</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81001</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>106757</t>
+          <t>106447</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>141851</t>
+          <t>141391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>22490</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40372</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13208</t>
+          <t>12709</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
